--- a/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
+++ b/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:37:28+00:00</t>
+    <t>2026-05-04T12:41:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
+++ b/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:41:26+00:00</t>
+    <t>2026-05-04T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
+++ b/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:53:37+00:00</t>
+    <t>2026-05-04T13:11:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
+++ b/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:11:55+00:00</t>
+    <t>2026-05-04T13:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
+++ b/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:17:58+00:00</t>
+    <t>2026-05-04T13:20:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
+++ b/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:20:45+00:00</t>
+    <t>2026-05-04T13:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
+++ b/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:31:24+00:00</t>
+    <t>2026-05-04T14:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
+++ b/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:06:39+00:00</t>
+    <t>2026-05-04T14:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
+++ b/nr-refacto-prescription/ig/CodeSystem-fr-additional-action-relationship-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:08:33+00:00</t>
+    <t>2026-05-04T14:21:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
